--- a/data/trans_dic/P1805_2016_2023-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P1805_2016_2023-Edad-trans_dic.xlsx
@@ -599,7 +599,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -609,7 +609,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>5,53%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -619,7 +619,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>4,99%</t>
         </is>
       </c>
     </row>
@@ -632,32 +632,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,92; 3,63</t>
+          <t>0,95; 4,08</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,63; 9,42</t>
+          <t>1,84; 9,08</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,94; 4,28</t>
+          <t>0,91; 4,47</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2,86; 10,74</t>
+          <t>2,75; 9,61</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,08; 3,15</t>
+          <t>1,14; 3,25</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,04; 8,52</t>
+          <t>2,81; 7,47</t>
         </is>
       </c>
     </row>
@@ -679,7 +679,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -689,7 +689,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,34%</t>
         </is>
       </c>
     </row>
@@ -712,32 +712,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,51; 2,88</t>
+          <t>0,53; 2,54</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,19; 5,2</t>
+          <t>1,3; 5,36</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,14; 3,58</t>
+          <t>1,15; 3,64</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,96; 6,14</t>
+          <t>2,32; 6,32</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,07; 2,6</t>
+          <t>1,09; 2,65</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,9; 4,77</t>
+          <t>2,17; 5,11</t>
         </is>
       </c>
     </row>
@@ -759,7 +759,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -769,7 +769,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -779,7 +779,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,17%</t>
         </is>
       </c>
     </row>
@@ -792,32 +792,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,55; 4,14</t>
+          <t>1,63; 4,09</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,72; 6,9</t>
+          <t>2,44; 6,35</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,09; 4,69</t>
+          <t>2,01; 4,82</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3,08; 6,21</t>
+          <t>3,13; 5,84</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2,1; 3,95</t>
+          <t>2,07; 3,87</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,38; 5,81</t>
+          <t>3,12; 5,36</t>
         </is>
       </c>
     </row>
@@ -839,7 +839,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>4,89%</t>
         </is>
       </c>
     </row>
@@ -872,32 +872,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,97; 3,25</t>
+          <t>0,98; 3,25</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,58; 6,12</t>
+          <t>3,62; 7,57</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,81; 6,32</t>
+          <t>2,84; 6,29</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3,25; 5,71</t>
+          <t>3,29; 5,84</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>2,13; 4,09</t>
+          <t>2,12; 4,1</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,42; 5,42</t>
+          <t>3,95; 6,28</t>
         </is>
       </c>
     </row>
@@ -919,7 +919,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -929,7 +929,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,05%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -939,7 +939,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>3,98%</t>
         </is>
       </c>
     </row>
@@ -952,32 +952,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,7; 3,58</t>
+          <t>0,66; 3,19</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,98; 4,66</t>
+          <t>1,85; 4,48</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3,68; 7,79</t>
+          <t>3,55; 7,82</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3,9; 6,87</t>
+          <t>3,92; 6,59</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2,55; 5,07</t>
+          <t>2,5; 5,08</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,36; 5,33</t>
+          <t>3,1; 5,04</t>
         </is>
       </c>
     </row>
@@ -999,7 +999,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -1009,7 +1009,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>2,1%</t>
         </is>
       </c>
     </row>
@@ -1032,32 +1032,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,29; 2,54</t>
+          <t>0,28; 2,83</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,33; 1,91</t>
+          <t>0,34; 1,78</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2,41; 7,08</t>
+          <t>2,4; 7,26</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,84; 3,97</t>
+          <t>2,23; 4,7</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1,78; 4,48</t>
+          <t>1,73; 4,59</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,83; 2,62</t>
+          <t>1,42; 3,04</t>
         </is>
       </c>
     </row>
@@ -1079,7 +1079,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,92%</t>
         </is>
       </c>
     </row>
@@ -1112,32 +1112,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,49; 3,68</t>
+          <t>0,35; 3,53</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,39; 2,35</t>
+          <t>0,35; 2,32</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2,57; 7,64</t>
+          <t>2,56; 8,09</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1,47; 3,75</t>
+          <t>1,53; 3,88</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1,91; 5,2</t>
+          <t>2,06; 5,29</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,28; 2,84</t>
+          <t>1,2; 2,9</t>
         </is>
       </c>
     </row>
@@ -1159,7 +1159,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -1169,7 +1169,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1179,7 +1179,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,78%</t>
         </is>
       </c>
     </row>
@@ -1192,32 +1192,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>1,4; 2,28</t>
+          <t>1,39; 2,31</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>2,41; 4,09</t>
+          <t>2,61; 4,08</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3,1; 4,54</t>
+          <t>3,07; 4,4</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3,12; 4,66</t>
+          <t>3,62; 4,86</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>2,41; 3,22</t>
+          <t>2,37; 3,22</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,1; 4,17</t>
+          <t>3,31; 4,26</t>
         </is>
       </c>
     </row>
@@ -1392,7 +1392,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>17955</t>
+          <t>18414</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -1402,7 +1402,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>18077</t>
+          <t>20055</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1412,7 +1412,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>36031</t>
+          <t>38470</t>
         </is>
       </c>
     </row>
@@ -1425,32 +1425,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>3845; 15212</t>
+          <t>3989; 17122</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>6532; 37660</t>
+          <t>7516; 37021</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3704; 16931</t>
+          <t>3614; 17674</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>8958; 33630</t>
+          <t>9971; 34845</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>8797; 25666</t>
+          <t>9332; 26501</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>21654; 60746</t>
+          <t>21608; 57543</t>
         </is>
       </c>
     </row>
@@ -1510,7 +1510,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>10803</t>
+          <t>12895</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>18332</t>
+          <t>19727</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1530,7 +1530,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>29134</t>
+          <t>32623</t>
         </is>
       </c>
     </row>
@@ -1543,32 +1543,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3033; 17006</t>
+          <t>3141; 15006</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>5036; 22009</t>
+          <t>6193; 25564</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6428; 20201</t>
+          <t>6485; 20533</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>10029; 31391</t>
+          <t>11614; 31654</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>12327; 29977</t>
+          <t>12531; 30533</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>17797; 44594</t>
+          <t>21199; 49955</t>
         </is>
       </c>
     </row>
@@ -1628,7 +1628,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>23400</t>
+          <t>24496</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1638,7 +1638,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>24758</t>
+          <t>27315</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1648,7 +1648,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>48158</t>
+          <t>51811</t>
         </is>
       </c>
     </row>
@@ -1661,32 +1661,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>10349; 27670</t>
+          <t>10894; 27390</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>14565; 37001</t>
+          <t>15143; 39399</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>13808; 31051</t>
+          <t>13309; 31887</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>16685; 33693</t>
+          <t>19463; 36356</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>27902; 52611</t>
+          <t>27528; 51554</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>36518; 62673</t>
+          <t>38757; 66612</t>
         </is>
       </c>
     </row>
@@ -1746,7 +1746,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>34528</t>
+          <t>36756</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>30806</t>
+          <t>33574</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1766,7 +1766,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>65335</t>
+          <t>70330</t>
         </is>
       </c>
     </row>
@@ -1779,32 +1779,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>6284; 20993</t>
+          <t>6324; 20989</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>13987; 54372</t>
+          <t>25359; 53016</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>18222; 41036</t>
+          <t>18418; 40812</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>23167; 40706</t>
+          <t>24263; 43025</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>27619; 52931</t>
+          <t>27419; 53059</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>38788; 86756</t>
+          <t>56810; 90224</t>
         </is>
       </c>
     </row>
@@ -1864,7 +1864,7 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>17689</t>
+          <t>17740</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -1874,7 +1874,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>28906</t>
+          <t>30705</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1884,7 +1884,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>46595</t>
+          <t>48445</t>
         </is>
       </c>
     </row>
@@ -1897,32 +1897,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>3352; 17107</t>
+          <t>3137; 15260</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>11122; 26158</t>
+          <t>11302; 27279</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>18301; 38697</t>
+          <t>17646; 38867</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>21329; 37580</t>
+          <t>23842; 40107</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>24839; 49377</t>
+          <t>24326; 49560</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>37206; 59105</t>
+          <t>37726; 61376</t>
         </is>
       </c>
     </row>
@@ -1982,7 +1982,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>3496</t>
+          <t>3533</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -1992,7 +1992,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>13309</t>
+          <t>14270</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2002,7 +2002,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>16805</t>
+          <t>17803</t>
         </is>
       </c>
     </row>
@@ -2015,32 +2015,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>963; 8495</t>
+          <t>925; 9462</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>1220; 7026</t>
+          <t>1366; 7236</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>9104; 26760</t>
+          <t>9067; 27423</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>5113; 24126</t>
+          <t>9775; 20633</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>12666; 31887</t>
+          <t>12336; 32657</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>8124; 25591</t>
+          <t>12030; 25687</t>
         </is>
       </c>
     </row>
@@ -2100,7 +2100,7 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>3053</t>
+          <t>3330</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -2110,7 +2110,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>10622</t>
+          <t>11545</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2120,7 +2120,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>13675</t>
+          <t>14875</t>
         </is>
       </c>
     </row>
@@ -2133,32 +2133,32 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>1247; 9451</t>
+          <t>896; 9065</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>1108; 6646</t>
+          <t>1073; 7206</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>10283; 30567</t>
+          <t>10247; 32357</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>6257; 15945</t>
+          <t>7097; 18001</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>12547; 34200</t>
+          <t>13538; 34738</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>9082; 20093</t>
+          <t>9300; 22463</t>
         </is>
       </c>
     </row>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>110924</t>
+          <t>117165</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -2228,7 +2228,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>144810</t>
+          <t>157192</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -2238,7 +2238,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>255734</t>
+          <t>274357</t>
         </is>
       </c>
     </row>
@@ -2251,32 +2251,32 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>47645; 77454</t>
+          <t>47184; 78455</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>83475; 141676</t>
+          <t>92163; 144233</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>110010; 160910</t>
+          <t>108863; 155830</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>114398; 170710</t>
+          <t>135152; 181297</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>167506; 223618</t>
+          <t>164728; 223541</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>220482; 297091</t>
+          <t>240328; 309782</t>
         </is>
       </c>
     </row>
